--- a/data/trans_orig/IP16A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Clase-trans_orig.xlsx
@@ -4745,7 +4745,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>25320</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52742</t>
+          <t>52420</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4195</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3325</t>
+          <t>3311</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>134963</t>
+          <t>136489</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282511</t>
+          <t>282525</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4198</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20654</t>
+          <t>20010</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>51662</t>
+          <t>50921</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10030,7 +10030,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10100,7 +10100,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10123,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25878</t>
+          <t>25295</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61225</t>
+          <t>61304</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>508</t>
+          <t>523</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>597</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>169229</t>
+          <t>169407</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>174879</t>
+          <t>174864</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>348769</t>
+          <t>348380</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354115</t>
+          <t>354100</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A07-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP16A07-Clase-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15171</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1179,47 +1179,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>17857</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>19430</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>17857</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1522,47 +1522,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>21952</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>11110</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>21952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1865,47 +1865,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>38789</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>37685</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>38789</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2208,47 +2208,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>23899</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>18853</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>23899</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2551,47 +2551,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2664,57 +2664,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>11337</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7484</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>11337</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2894,47 +2894,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3007,57 +3007,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135297</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>109734</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135297</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3179,7 +3179,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3190,7 +3190,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3471,47 +3471,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>20920</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -3584,57 +3584,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>21978</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>20920</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>21978</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3814,47 +3814,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22903</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -3927,57 +3927,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12088</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>22903</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>22903</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>22903</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>12088</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4157,47 +4157,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>10991</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4270,57 +4270,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>12478</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>10991</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>10991</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>10991</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>12478</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4500,47 +4500,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>48643</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -4613,57 +4613,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>58910</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>48643</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>48643</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>48643</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>58910</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4730,107 +4730,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3325</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3120</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,29%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,17%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3654</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -4843,74 +4843,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>27429</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>27989</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>25320</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25525</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,71%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>89,11%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27429</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>77</t>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>52420</t>
+          <t>52069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -4938,7 +4938,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4956,57 +4956,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27429</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27429</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27429</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>28645</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>27429</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>27429</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>27429</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5186,47 +5186,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>7056</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -5299,57 +5299,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>13795</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>7056</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>13795</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5416,107 +5416,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2669</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2963</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3311</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
     </row>
@@ -5529,74 +5529,74 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>146679</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>200</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138502</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>136489</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>136195</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>139158</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>98,08%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>146679</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>406</t>
@@ -5609,7 +5609,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>282525</t>
+          <t>282576</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -5624,7 +5624,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -5642,57 +5642,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>146679</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>146679</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>146679</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>139158</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>139158</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>139158</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>206</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>146679</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>146679</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>146679</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5814,7 +5814,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5825,7 +5825,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6106,47 +6106,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15843</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -6219,57 +6219,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>17744</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>15843</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>17744</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6449,47 +6449,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>11996</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -6562,57 +6562,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19062</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>11996</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>19062</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6792,47 +6792,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>8846</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -6905,57 +6905,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>10267</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>8846</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>10267</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7135,47 +7135,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>46489</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -7248,57 +7248,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>34524</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>46489</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>34524</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7478,47 +7478,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>26621</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -7591,57 +7591,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>25662</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>26621</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25662</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7821,47 +7821,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -7934,57 +7934,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>9778</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>13025</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>9778</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8164,47 +8164,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>122820</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -8277,57 +8277,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>117035</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>122820</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>117035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -8460,7 +8460,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -8628,107 +8628,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4842</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,65%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4464</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5,71%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1407</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5174</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1405</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5332</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,68%</t>
         </is>
       </c>
     </row>
@@ -8746,69 +8746,69 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23447</t>
+          <t>28840</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>23231</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20174</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>24638</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>94,29%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31401</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>78</t>
@@ -8816,27 +8816,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54848</t>
+          <t>52071</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>48304</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8854,57 +8854,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28840</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>24852</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31401</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>56253</t>
+          <t>53478</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9084,64 +9084,64 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>22976</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>23492</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -9197,57 +9197,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>22626</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>23432</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>22976</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>46924</t>
+          <t>45602</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9427,64 +9427,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>9519</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>17296</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -9502,7 +9502,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -9540,57 +9540,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15025</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9596</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17296</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>26892</t>
+          <t>24544</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9770,64 +9770,64 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>42540</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>55844</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
@@ -9883,57 +9883,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>49744</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>76381</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55844</t>
+          <t>42540</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>132225</t>
+          <t>92285</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10000,107 +10000,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3611</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,47%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3268</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>11,42%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>653</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3706</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>713</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>3579</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -10113,74 +10113,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>28193</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>25295</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>97,53%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>87,51%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>27961</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>25346</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>97,72%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>88,58%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>35977</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>95</t>
@@ -10188,27 +10188,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>64170</t>
+          <t>60132</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>61304</t>
+          <t>57079</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -10226,57 +10226,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>32170</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>28906</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>35977</t>
+          <t>28614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12221</t>
+          <t>14115</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>15299</t>
+          <t>12449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>27520</t>
+          <t>26564</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10686,72 +10686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>523</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>5980</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5827</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>552</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6317</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,95%</t>
         </is>
       </c>
     </row>
@@ -10799,72 +10799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>173269</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>169407</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>174864</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>99,7%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>138675</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>134909</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>140190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>352579</t>
+          <t>301196</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>348380</t>
+          <t>297345</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>354100</t>
+          <t>302705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -10912,57 +10912,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>162520</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>175387</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>179309</t>
+          <t>140736</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>354697</t>
+          <t>303257</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
